--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_16/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_16/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63.43523565859909</v>
+        <v>99.99999426625689</v>
       </c>
       <c r="B2" t="n">
-        <v>82.86316683108906</v>
+        <v>56.09599313315874</v>
       </c>
       <c r="C2" t="n">
-        <v>48.78422229089842</v>
+        <v>45.42047641229109</v>
       </c>
       <c r="D2" t="n">
-        <v>7.100137676392178</v>
+        <v>9.894103441301255</v>
       </c>
       <c r="E2" t="n">
-        <v>2.716724633791615</v>
+        <v>4.528904031488849</v>
       </c>
       <c r="F2" t="n">
-        <v>9.313027057873045</v>
+        <v>16.56389773664896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2145231243156965</v>
+        <v>0.04280312287358865</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0004683429073674144</v>
+        <v>-0.6928192820965698</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6318721182154496</v>
+        <v>-0.8582158655141991</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.508912377910588</v>
+        <v>-0.8970994078880029</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.7572627877126e-05</v>
+        <v>-0.0001848073214400756</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6712138966266086</v>
+        <v>-0.5874999591470803</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07705618530837141</v>
+        <v>-0.0008312172271458806</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999999808367</v>
+        <v>99.99999426625689</v>
       </c>
       <c r="B3" t="n">
-        <v>199.9530282676197</v>
+        <v>56.09599313315874</v>
       </c>
       <c r="C3" t="n">
-        <v>48.79262002485068</v>
+        <v>45.42047641229109</v>
       </c>
       <c r="D3" t="n">
-        <v>8.634751088751715</v>
+        <v>9.894103441301255</v>
       </c>
       <c r="E3" t="n">
-        <v>3.825320980381524</v>
+        <v>4.626604474937089</v>
       </c>
       <c r="F3" t="n">
-        <v>16.20286763051222</v>
+        <v>16.56389773664896</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04348298960747325</v>
+        <v>0.04280312287358865</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7308939582373597</v>
+        <v>-0.6928192820965698</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8735389186983776</v>
+        <v>-0.8582158655141991</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9135381070919651</v>
+        <v>-0.8970994078880029</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.003394731310899335</v>
+        <v>-0.0001848073214400756</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069729797207</v>
+        <v>-0.5874999591470803</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07762968843894451</v>
+        <v>-0.0008312172271458806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63.43523565859909</v>
+        <v>66.72204180882061</v>
       </c>
       <c r="B4" t="n">
-        <v>82.86316683108906</v>
+        <v>38.08377189014391</v>
       </c>
       <c r="C4" t="n">
-        <v>48.78422229089842</v>
+        <v>45.41746335793211</v>
       </c>
       <c r="D4" t="n">
-        <v>7.100137676392178</v>
+        <v>6.469494530974315</v>
       </c>
       <c r="E4" t="n">
-        <v>2.42266041762278</v>
+        <v>2.10992173247367</v>
       </c>
       <c r="F4" t="n">
-        <v>9.313027057873045</v>
+        <v>9.978174847141487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2145231243156965</v>
+        <v>0.1739721108204294</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0004683429073674144</v>
+        <v>-0.01693674328383978</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6318721182154496</v>
+        <v>-0.6369903004766894</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.508912377910588</v>
+        <v>-0.5206527984196355</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.7572627877126e-05</v>
+        <v>-0.0001516477460967912</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6712138966266086</v>
+        <v>-0.03941705151666346</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07705618530837141</v>
+        <v>-0.0001738235488236983</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77.46508483330975</v>
+        <v>72.2977848199522</v>
       </c>
       <c r="B5" t="n">
-        <v>117.7660003442916</v>
+        <v>55.39572020287083</v>
       </c>
       <c r="C5" t="n">
-        <v>48.78571555318139</v>
+        <v>45.42072941612676</v>
       </c>
       <c r="D5" t="n">
-        <v>12.60601099818065</v>
+        <v>5.928879464873642</v>
       </c>
       <c r="E5" t="n">
-        <v>4.762299615185212</v>
+        <v>2.199265533803752</v>
       </c>
       <c r="F5" t="n">
-        <v>11.58799298038782</v>
+        <v>11.30679350848347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1088893854049401</v>
+        <v>0.1295927479919989</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4357744583716973</v>
+        <v>-0.2209800965474081</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7649233844599285</v>
+        <v>-0.6973892538164641</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7693102660799414</v>
+        <v>-0.6477360407759858</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01630809221160873</v>
+        <v>-0.00356446678844001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4536695853405693</v>
+        <v>-0.6261033750688971</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07715816408013527</v>
+        <v>-0.000886418064020289</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76.00872431346924</v>
+        <v>81.8931524447881</v>
       </c>
       <c r="B6" t="n">
-        <v>123.5830056262728</v>
+        <v>71.72532830742719</v>
       </c>
       <c r="C6" t="n">
-        <v>48.8307535003974</v>
+        <v>46.52574038207137</v>
       </c>
       <c r="D6" t="n">
-        <v>12.71681208359696</v>
+        <v>12.08099376896894</v>
       </c>
       <c r="E6" t="n">
-        <v>4.053558163994591</v>
+        <v>2.206416134031961</v>
       </c>
       <c r="F6" t="n">
-        <v>11.30511111201862</v>
+        <v>12.51629140461601</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1167684189508133</v>
+        <v>0.08706929653034606</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4035777100911757</v>
+        <v>-0.456561325508986</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7541171232726517</v>
+        <v>-0.7729801629760953</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7516781240865164</v>
+        <v>-0.7813020474553458</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.001489318986443909</v>
+        <v>-0.00123864315272029</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4427904707054285</v>
+        <v>-0.4512967273925156</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0802339228347953</v>
+        <v>-0.2419797197246629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69.05560769628474</v>
+        <v>98.18844703699305</v>
       </c>
       <c r="B7" t="n">
-        <v>82.75198617324507</v>
+        <v>69.744656757592</v>
       </c>
       <c r="C7" t="n">
-        <v>48.78035864165354</v>
+        <v>45.43596500968627</v>
       </c>
       <c r="D7" t="n">
-        <v>5.68202191807583</v>
+        <v>10.62892461342687</v>
       </c>
       <c r="E7" t="n">
-        <v>2.185663203209227</v>
+        <v>3.767065700638401</v>
       </c>
       <c r="F7" t="n">
-        <v>10.35000670271173</v>
+        <v>16.23745324899949</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1562287514914427</v>
+        <v>0.04566969346017077</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2213673454845296</v>
+        <v>-0.6760930037455685</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6976946743501711</v>
+        <v>-0.8516300817632434</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6475527081468707</v>
+        <v>-0.8896062935764774</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.203650301157601e-05</v>
+        <v>-0.07414125279418386</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7085335153196917</v>
+        <v>-0.5745926851385754</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07679232663530902</v>
+        <v>-0.004210547567912865</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67.54964072244471</v>
+        <v>96.10044063187338</v>
       </c>
       <c r="B8" t="n">
-        <v>58.94477182043742</v>
+        <v>55.80610679803853</v>
       </c>
       <c r="C8" t="n">
-        <v>48.78128934371563</v>
+        <v>45.44516329554487</v>
       </c>
       <c r="D8" t="n">
-        <v>6.111455582611343</v>
+        <v>10.74958748548276</v>
       </c>
       <c r="E8" t="n">
-        <v>4.932254329731843</v>
+        <v>3.541829216574003</v>
       </c>
       <c r="F8" t="n">
-        <v>10.07296946207628</v>
+        <v>15.6940807744623</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1695831664204019</v>
+        <v>0.0492034357597373</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1692540531655463</v>
+        <v>-0.6554251859243145</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6817513607859973</v>
+        <v>-0.8436588607697825</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6158894640543778</v>
+        <v>-0.88018616525436</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.005596449281314615</v>
+        <v>-0.02778569001533542</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.698533801270294</v>
+        <v>-0.5597156395020977</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07685588670392648</v>
+        <v>-0.006217446300699619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83.11674582023083</v>
+        <v>77.35798631962457</v>
       </c>
       <c r="B9" t="n">
-        <v>197.6955692392467</v>
+        <v>67.63537684484962</v>
       </c>
       <c r="C9" t="n">
-        <v>48.78423879486206</v>
+        <v>45.42014446652426</v>
       </c>
       <c r="D9" t="n">
-        <v>11.77841025423502</v>
+        <v>5.006585979539228</v>
       </c>
       <c r="E9" t="n">
-        <v>3.992988194567907</v>
+        <v>2.238929021533505</v>
       </c>
       <c r="F9" t="n">
-        <v>12.65361010992705</v>
+        <v>12.50801990715341</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08409453293107445</v>
+        <v>0.1013677886830934</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5406526496291452</v>
+        <v>-0.3608815361038979</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8013499992867892</v>
+        <v>-0.7416704720310532</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.824404238775894</v>
+        <v>-0.7291038566004414</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02161225730412155</v>
+        <v>-0.2690367035191903</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4958878870028534</v>
+        <v>-0.3899606384175195</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07705731240704615</v>
+        <v>-0.0007587926962028535</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69.73508528487221</v>
+        <v>72.85429488048999</v>
       </c>
       <c r="B10" t="n">
-        <v>82.04374985509658</v>
+        <v>68.30786709808201</v>
       </c>
       <c r="C10" t="n">
-        <v>48.78436284795742</v>
+        <v>45.42580785259683</v>
       </c>
       <c r="D10" t="n">
-        <v>5.779345793543745</v>
+        <v>6.394194054067087</v>
       </c>
       <c r="E10" t="n">
-        <v>4.125139989470186</v>
+        <v>2.243091712349652</v>
       </c>
       <c r="F10" t="n">
-        <v>10.5510284984228</v>
+        <v>11.57336153145669</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1507778856518401</v>
+        <v>0.1261829594716064</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2432946545218918</v>
+        <v>-0.2380407940745143</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7044631718511271</v>
+        <v>-0.7026216289791246</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6606535314518158</v>
+        <v>-0.6579084438799289</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.09897933777737719</v>
+        <v>-0.1881494441882793</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7130452886234074</v>
+        <v>-0.6001329055771339</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07706578431612983</v>
+        <v>-0.001994440566581018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>85.07149141042875</v>
+        <v>69.48951503824155</v>
       </c>
       <c r="B11" t="n">
-        <v>81.19854449032918</v>
+        <v>45.86832532590832</v>
       </c>
       <c r="C11" t="n">
-        <v>49.19774610436151</v>
+        <v>45.42814799393339</v>
       </c>
       <c r="D11" t="n">
-        <v>11.48073964841007</v>
+        <v>6.659965831231117</v>
       </c>
       <c r="E11" t="n">
-        <v>4.391964647264499</v>
+        <v>4.822120489386954</v>
       </c>
       <c r="F11" t="n">
-        <v>13.05592667331887</v>
+        <v>10.73582933613286</v>
       </c>
       <c r="G11" t="n">
-        <v>0.07730532890771112</v>
+        <v>0.1499721803512721</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5706745183365001</v>
+        <v>-0.124784196870639</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8121495963117251</v>
+        <v>-0.6681569609198962</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.839457771534296</v>
+        <v>-0.5888340208385682</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03236559108244173</v>
+        <v>-0.001316017482846544</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5104899728659252</v>
+        <v>-0.6901002619088632</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1031179999396929</v>
+        <v>-0.00250501685819457</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63.79923070969922</v>
+        <v>92.81046018767641</v>
       </c>
       <c r="B12" t="n">
-        <v>83.10657956087709</v>
+        <v>59.44057314411369</v>
       </c>
       <c r="C12" t="n">
-        <v>48.82768035498887</v>
+        <v>45.42013006578996</v>
       </c>
       <c r="D12" t="n">
-        <v>7.087564157930802</v>
+        <v>10.76538955990238</v>
       </c>
       <c r="E12" t="n">
-        <v>4.673633614371456</v>
+        <v>4.832124258694789</v>
       </c>
       <c r="F12" t="n">
-        <v>9.398111361127102</v>
+        <v>14.81785986234395</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2100120505966664</v>
+        <v>0.05553607100451235</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.01712959049709354</v>
+        <v>-0.6220149986756932</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6366788287047191</v>
+        <v>-0.8317872455048694</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5197519520436671</v>
+        <v>-0.8648232225846704</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.02069656899374574</v>
+        <v>-0.002896772610967546</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.673630846327116</v>
+        <v>-0.0813361254092182</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.08002404972825045</v>
+        <v>-0.0007556507178098359</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83.88772072595523</v>
+        <v>83.04613435378941</v>
       </c>
       <c r="B13" t="n">
-        <v>75.09812330705779</v>
+        <v>72.61444795241835</v>
       </c>
       <c r="C13" t="n">
-        <v>47.33629492355558</v>
+        <v>45.42053838982065</v>
       </c>
       <c r="D13" t="n">
-        <v>11.82747545810806</v>
+        <v>12.09416353008368</v>
       </c>
       <c r="E13" t="n">
-        <v>2.358627534075314</v>
+        <v>4.651607599830418</v>
       </c>
       <c r="F13" t="n">
-        <v>12.93661584383952</v>
+        <v>12.71627044722108</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08124800636271495</v>
+        <v>0.08270884189494962</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5529255030103176</v>
+        <v>-0.4782815703002219</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8057631603429952</v>
+        <v>-0.780413494247474</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8306102752699811</v>
+        <v>-0.7928196139948589</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.05943256732657458</v>
+        <v>-0.01025038064628347</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5000399475080406</v>
+        <v>-0.4013341780024587</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08333629919453886</v>
+        <v>-0.0008447395972317751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72.13337181486351</v>
+        <v>88.1218820677929</v>
       </c>
       <c r="B14" t="n">
-        <v>36.88138479072055</v>
+        <v>65.36086466660448</v>
       </c>
       <c r="C14" t="n">
-        <v>49.06165667152078</v>
+        <v>47.03426510016157</v>
       </c>
       <c r="D14" t="n">
-        <v>5.007727408889416</v>
+        <v>11.04248891295846</v>
       </c>
       <c r="E14" t="n">
-        <v>3.847047254209012</v>
+        <v>2.147353362553477</v>
       </c>
       <c r="F14" t="n">
-        <v>10.99718415340461</v>
+        <v>13.78279595683137</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1330550502511608</v>
+        <v>0.06678614837971199</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3147328652742007</v>
+        <v>-0.5608745618925968</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.726976474547141</v>
+        <v>-0.809419772279525</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7025100845231073</v>
+        <v>-0.8351287671434605</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1132992143038361</v>
+        <v>-0.01105132591975439</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7204420277266543</v>
+        <v>-0.1813851103956414</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09414485575810931</v>
+        <v>-0.3529305673079787</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>71.4568109689384</v>
+        <v>68.46201403193709</v>
       </c>
       <c r="B15" t="n">
-        <v>53.78523796647355</v>
+        <v>43.02904946783223</v>
       </c>
       <c r="C15" t="n">
-        <v>49.31068961396716</v>
+        <v>45.41881834679617</v>
       </c>
       <c r="D15" t="n">
-        <v>5.24025382703922</v>
+        <v>6.483128479845926</v>
       </c>
       <c r="E15" t="n">
-        <v>2.36008566251275</v>
+        <v>4.80268085304585</v>
       </c>
       <c r="F15" t="n">
-        <v>10.87687841979208</v>
+        <v>10.42493872955291</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1377710491327233</v>
+        <v>0.158295726421447</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2955342556978734</v>
+        <v>-0.08844483099661289</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7208653796140683</v>
+        <v>-0.6578521348528875</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6913959961381991</v>
+        <v>-0.5663730918572444</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1157193404189476</v>
+        <v>-0.006725972505118786</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7224442896273006</v>
+        <v>-0.0400452779024905</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1072751313141446</v>
+        <v>-0.000469457482801805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>86.06413293614327</v>
+        <v>84.23051074127969</v>
       </c>
       <c r="B16" t="n">
-        <v>75.09812330705779</v>
+        <v>68.3391733158313</v>
       </c>
       <c r="C16" t="n">
-        <v>47.33629492355558</v>
+        <v>46.56946354891046</v>
       </c>
       <c r="D16" t="n">
-        <v>11.82747545810806</v>
+        <v>11.78949071638648</v>
       </c>
       <c r="E16" t="n">
-        <v>2.357079037019857</v>
+        <v>4.839236949644354</v>
       </c>
       <c r="F16" t="n">
-        <v>13.35430417936885</v>
+        <v>12.99477082232005</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07424535662032823</v>
+        <v>0.07861801169873432</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5847479016602305</v>
+        <v>-0.4993123704640273</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8172414107882705</v>
+        <v>-0.7876731662333835</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8463838309848324</v>
+        <v>-0.8038154331654996</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.07908148907675377</v>
+        <v>-0.01659935898529056</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5179050742798471</v>
+        <v>-0.3500112012112133</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08333629919453886</v>
+        <v>-0.2515193197622834</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95.62025290787972</v>
+        <v>71.23867608501897</v>
       </c>
       <c r="B17" t="n">
-        <v>96.39080878948533</v>
+        <v>60.80312330475766</v>
       </c>
       <c r="C17" t="n">
-        <v>48.84058389142312</v>
+        <v>45.42046416255148</v>
       </c>
       <c r="D17" t="n">
-        <v>9.500326666339824</v>
+        <v>6.210760868046658</v>
       </c>
       <c r="E17" t="n">
-        <v>4.334817695455098</v>
+        <v>4.825683772622324</v>
       </c>
       <c r="F17" t="n">
-        <v>15.22034906332842</v>
+        <v>11.08936990526789</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0508623707202769</v>
+        <v>0.1368210846466374</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6939549353063109</v>
+        <v>-0.1864720472076336</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.858748916437427</v>
+        <v>-0.6867966316953467</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8974890340894477</v>
+        <v>-0.6268683094328988</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.001391745582742401</v>
+        <v>-0.00125394879934298</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.589289956816394</v>
+        <v>-0.6755284493657815</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0809052658494767</v>
+        <v>-0.0008285445566875993</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>74.51844972953648</v>
+        <v>71.23867608501897</v>
       </c>
       <c r="B18" t="n">
-        <v>172.6809134752927</v>
+        <v>47.67618466536965</v>
       </c>
       <c r="C18" t="n">
-        <v>48.78423797019091</v>
+        <v>45.42046416255148</v>
       </c>
       <c r="D18" t="n">
-        <v>12.93052857357637</v>
+        <v>6.210760868046658</v>
       </c>
       <c r="E18" t="n">
-        <v>2.515797965695733</v>
+        <v>4.825683772622324</v>
       </c>
       <c r="F18" t="n">
-        <v>11.04094413352366</v>
+        <v>11.08936990526789</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1256779487115234</v>
+        <v>0.1368210846466374</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3679256369582298</v>
+        <v>-0.1864720472076336</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7423165716318419</v>
+        <v>-0.6867966316953467</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7317774614652346</v>
+        <v>-0.6268683094328988</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0008073680994999921</v>
+        <v>-0.00125394879934298</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4316580156466929</v>
+        <v>-0.6755284493657815</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0770572560881054</v>
+        <v>-0.0008285445566875993</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>64.88114301437597</v>
+        <v>70.31369496067053</v>
       </c>
       <c r="B19" t="n">
-        <v>62.8427394502382</v>
+        <v>74.13543173180362</v>
       </c>
       <c r="C19" t="n">
-        <v>47.99362510813605</v>
+        <v>45.43241613880921</v>
       </c>
       <c r="D19" t="n">
-        <v>7.074106090495252</v>
+        <v>6.476431139584568</v>
       </c>
       <c r="E19" t="n">
-        <v>3.790907627617217</v>
+        <v>3.974359599339122</v>
       </c>
       <c r="F19" t="n">
-        <v>9.666012424728065</v>
+        <v>10.90814557855942</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1973457695555648</v>
+        <v>0.1435866602657368</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.06445233509878245</v>
+        <v>-0.1545997256883735</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6504501268324885</v>
+        <v>-0.6771176257082501</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.550202798911653</v>
+        <v>-0.6073302410199928</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.07073856121214098</v>
+        <v>-0.008905818791326205</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6808148110894412</v>
+        <v>-0.6953200680842466</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07650065724859897</v>
+        <v>-0.003436248467464098</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>65.42056489964453</v>
+        <v>68.8504446608034</v>
       </c>
       <c r="B20" t="n">
-        <v>74.89097413224749</v>
+        <v>45.86302638078178</v>
       </c>
       <c r="C20" t="n">
-        <v>48.78350988620803</v>
+        <v>46.18248189536576</v>
       </c>
       <c r="D20" t="n">
-        <v>6.640372588998101</v>
+        <v>6.361974189103123</v>
       </c>
       <c r="E20" t="n">
-        <v>4.311390247752578</v>
+        <v>4.479539184065576</v>
       </c>
       <c r="F20" t="n">
-        <v>9.676181214326673</v>
+        <v>10.52199631295857</v>
       </c>
       <c r="G20" t="n">
-        <v>0.19111310299681</v>
+        <v>0.1550454387140875</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.08719854843783433</v>
+        <v>-0.10344324704748</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6571882847640952</v>
+        <v>-0.6622847577974891</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5646998132267769</v>
+        <v>-0.5758169578397405</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001999741041830364</v>
+        <v>-0.0175070464940118</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6843966058421631</v>
+        <v>-0.02466989884319907</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07700753333600661</v>
+        <v>-0.167086958988894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96.75709853228807</v>
+        <v>74.93801777324558</v>
       </c>
       <c r="B21" t="n">
-        <v>58.62313141701236</v>
+        <v>43.97905362889126</v>
       </c>
       <c r="C21" t="n">
-        <v>48.84058389142312</v>
+        <v>45.4338042995362</v>
       </c>
       <c r="D21" t="n">
-        <v>9.500326666339824</v>
+        <v>5.254955471070101</v>
       </c>
       <c r="E21" t="n">
-        <v>4.957859318391284</v>
+        <v>3.967925817770506</v>
       </c>
       <c r="F21" t="n">
-        <v>15.52726466020041</v>
+        <v>11.87462152550802</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04882609547713124</v>
+        <v>0.1136677229611298</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7041337667010008</v>
+        <v>-0.298743394243911</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8627651894052882</v>
+        <v>-0.7217295729870193</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9019746926308166</v>
+        <v>-0.6936301859293957</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04705418839934241</v>
+        <v>-0.0476184220029674</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5977822729029021</v>
+        <v>-0.5028925039152066</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0809052658494767</v>
+        <v>-0.003739119898807236</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>70.84038098358165</v>
+        <v>86.8544265489093</v>
       </c>
       <c r="B22" t="n">
-        <v>40.84360359750106</v>
+        <v>64.51231473849376</v>
       </c>
       <c r="C22" t="n">
-        <v>49.36557131840397</v>
+        <v>45.41918768660017</v>
       </c>
       <c r="D22" t="n">
-        <v>5.24025382703922</v>
+        <v>11.41963683511066</v>
       </c>
       <c r="E22" t="n">
-        <v>3.415774048732572</v>
+        <v>4.050836370067579</v>
       </c>
       <c r="F22" t="n">
-        <v>10.7142227745441</v>
+        <v>13.46546387830766</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1421831155122026</v>
+        <v>0.07029814884836891</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.277488388184774</v>
+        <v>-0.5420654683748835</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7151782266004686</v>
+        <v>-0.8027078347018655</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.680867652827827</v>
+        <v>-0.8257100637683528</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.04526260118606595</v>
+        <v>-0.004479615877060015</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7196570925772713</v>
+        <v>-0.2363081828805969</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1074145740301584</v>
+        <v>-0.0005500407127638496</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>65.9130448558776</v>
+        <v>73.67739016214151</v>
       </c>
       <c r="B23" t="n">
-        <v>53.04962460125667</v>
+        <v>36.67932912747668</v>
       </c>
       <c r="C23" t="n">
-        <v>49.18525648197146</v>
+        <v>45.53403659493539</v>
       </c>
       <c r="D23" t="n">
-        <v>6.48706055143391</v>
+        <v>5.516383521960214</v>
       </c>
       <c r="E23" t="n">
-        <v>4.706871167570324</v>
+        <v>4.069101109039173</v>
       </c>
       <c r="F23" t="n">
-        <v>9.767184101652218</v>
+        <v>11.58860276057045</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1858292813939933</v>
+        <v>0.1209111651418003</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.107123288086273</v>
+        <v>-0.2630218132158754</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.663095485921536</v>
+        <v>-0.7104678143378474</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5772753377167937</v>
+        <v>-0.6727490833829648</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0002240604488448391</v>
+        <v>-0.001208640369960196</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6876667032765266</v>
+        <v>-0.5617217924333964</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1025625502014237</v>
+        <v>-0.02560798434954048</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89.81242959047849</v>
+        <v>91.86484077197152</v>
       </c>
       <c r="B24" t="n">
-        <v>76.96458089423909</v>
+        <v>43.97905362889126</v>
       </c>
       <c r="C24" t="n">
-        <v>47.43093189105959</v>
+        <v>45.42008134864596</v>
       </c>
       <c r="D24" t="n">
-        <v>10.70804187202856</v>
+        <v>10.64228127288994</v>
       </c>
       <c r="E24" t="n">
-        <v>2.677673498605935</v>
+        <v>3.976962093590426</v>
       </c>
       <c r="F24" t="n">
-        <v>14.0046705869372</v>
+        <v>14.54078150130931</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0635681108585535</v>
+        <v>0.05753473836002411</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6332182154979699</v>
+        <v>-0.6107067104094561</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8353073823400767</v>
+        <v>-0.8275948746584242</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8697031465546118</v>
+        <v>-0.8594455454349452</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.001206924979371895</v>
+        <v>-0.02725343214515788</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5459051116562333</v>
+        <v>-0.01919023321456807</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.08694403804476446</v>
+        <v>-0.0007450215227536305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81.05304308263514</v>
+        <v>75.61588807138895</v>
       </c>
       <c r="B25" t="n">
-        <v>87.83195353601387</v>
+        <v>72.57352096532897</v>
       </c>
       <c r="C25" t="n">
-        <v>47.33879520114911</v>
+        <v>45.42049698431104</v>
       </c>
       <c r="D25" t="n">
-        <v>12.15794239755277</v>
+        <v>5.204794243275164</v>
       </c>
       <c r="E25" t="n">
-        <v>3.736284727056357</v>
+        <v>2.233484213602025</v>
       </c>
       <c r="F25" t="n">
-        <v>12.26194716004471</v>
+        <v>12.05431189596168</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09219665648218552</v>
+        <v>0.1100344661873238</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5056956665572171</v>
+        <v>-0.3169442364893847</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7889879316573155</v>
+        <v>-0.7275188541174287</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8064571547733238</v>
+        <v>-0.7041319132553562</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.001427531387193953</v>
+        <v>-0.111454080839695</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4804718836511447</v>
+        <v>-0.4712585566685161</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08343161446983169</v>
+        <v>-0.0008357056678631736</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>77.86859079995139</v>
+        <v>67.41106256274905</v>
       </c>
       <c r="B26" t="n">
-        <v>117.7660003442916</v>
+        <v>36.57105979191308</v>
       </c>
       <c r="C26" t="n">
-        <v>48.19166581466067</v>
+        <v>45.56462699617015</v>
       </c>
       <c r="D26" t="n">
-        <v>12.95831427547438</v>
+        <v>6.361974189103123</v>
       </c>
       <c r="E26" t="n">
-        <v>4.704740264991448</v>
+        <v>4.479539184065576</v>
       </c>
       <c r="F26" t="n">
-        <v>11.80053648383338</v>
+        <v>10.13106930212433</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1070965686466935</v>
+        <v>0.1674869331767377</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4439457006917709</v>
+        <v>-0.04616290969903779</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7676212994858708</v>
+        <v>-0.6454694942429231</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7737003259970952</v>
+        <v>-0.5394805651200575</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0663486408512293</v>
+        <v>-0.0283765305017113</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4566838030478294</v>
+        <v>-0.01142558338832015</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.06913873170537937</v>
+        <v>-0.03228225370985119</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94.7205755044604</v>
+        <v>87.37865587761408</v>
       </c>
       <c r="B27" t="n">
-        <v>186.1201763712189</v>
+        <v>66.37275993865696</v>
       </c>
       <c r="C27" t="n">
-        <v>47.19850581403198</v>
+        <v>45.42014298315722</v>
       </c>
       <c r="D27" t="n">
-        <v>9.831112939217153</v>
+        <v>11.37574912575016</v>
       </c>
       <c r="E27" t="n">
-        <v>4.815597313614785</v>
+        <v>4.43393927482265</v>
       </c>
       <c r="F27" t="n">
-        <v>15.05067716468584</v>
+        <v>13.5838846883177</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05260680695197786</v>
+        <v>0.0688031782397676</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6854778212356257</v>
+        <v>-0.5499853260013311</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8554073761641104</v>
+        <v>-0.8055273674066107</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8937096778311482</v>
+        <v>-0.8296925938852504</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0001344510173185552</v>
+        <v>-0.01268632277959765</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5825693038783999</v>
+        <v>-0.213591578636723</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07825893017863697</v>
+        <v>-0.000758469052484223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>71.72412964460273</v>
+        <v>70.28369218555353</v>
       </c>
       <c r="B28" t="n">
-        <v>123.5830056262728</v>
+        <v>74.13543173180362</v>
       </c>
       <c r="C28" t="n">
-        <v>49.05530177091538</v>
+        <v>45.43241613880921</v>
       </c>
       <c r="D28" t="n">
-        <v>13.47731619620577</v>
+        <v>6.476431139584568</v>
       </c>
       <c r="E28" t="n">
-        <v>4.05206594691858</v>
+        <v>3.963852494898973</v>
       </c>
       <c r="F28" t="n">
-        <v>10.61342587280217</v>
+        <v>10.90019424816408</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1451094468696044</v>
+        <v>0.1438102560758424</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2926575420296744</v>
+        <v>-0.153542276029773</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7179258579266951</v>
+        <v>-0.6767989973812873</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6885259327389759</v>
+        <v>-0.6066783290466314</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02941884296377911</v>
+        <v>-0.006546004632924803</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.4107842497644649</v>
+        <v>-0.6951300505085056</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0937063935692151</v>
+        <v>-0.003436248467464098</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87.69131881649639</v>
+        <v>74.08281690579804</v>
       </c>
       <c r="B29" t="n">
-        <v>83.69037780418101</v>
+        <v>43.2574810090175</v>
       </c>
       <c r="C29" t="n">
-        <v>48.78410205594179</v>
+        <v>45.42402285338975</v>
       </c>
       <c r="D29" t="n">
-        <v>10.94554732451241</v>
+        <v>5.516383521960214</v>
       </c>
       <c r="E29" t="n">
-        <v>2.538695283891665</v>
+        <v>4.094318914946456</v>
       </c>
       <c r="F29" t="n">
-        <v>13.54091967053917</v>
+        <v>11.6982456552589</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06923367193719074</v>
+        <v>0.1185364788049212</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6069495817963689</v>
+        <v>-0.2747442981916988</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.825482778748416</v>
+        <v>-0.7141413647245971</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8571964474579967</v>
+        <v>-0.6796356359005482</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.006098287330496308</v>
+        <v>-0.04275201346751999</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5300602662696593</v>
+        <v>-0.5428018777294251</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07704797414993064</v>
+        <v>-0.001604986194127106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>64.37015969314599</v>
+        <v>94.53946276461447</v>
       </c>
       <c r="B30" t="n">
-        <v>80.97807957500332</v>
+        <v>65.70229576422733</v>
       </c>
       <c r="C30" t="n">
-        <v>48.78709916083871</v>
+        <v>45.42014298648863</v>
       </c>
       <c r="D30" t="n">
-        <v>7.100137676392178</v>
+        <v>11.19035509132485</v>
       </c>
       <c r="E30" t="n">
-        <v>2.862040186519912</v>
+        <v>4.147840590405083</v>
       </c>
       <c r="F30" t="n">
-        <v>9.536709571245501</v>
+        <v>15.3800345150996</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2031937528180303</v>
+        <v>0.05215057391952437</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.04250218161306772</v>
+        <v>-0.6386580392943747</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6440402109385104</v>
+        <v>-0.8372483417466334</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5361410244420682</v>
+        <v>-0.8723966388748361</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.05984037081025765</v>
+        <v>-0.0558816812508553</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.6774218501646196</v>
+        <v>-0.548593672197878</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.07725265425182533</v>
+        <v>-0.0007584697793371065</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>68.12597562850561</v>
+        <v>66.76695361216431</v>
       </c>
       <c r="B31" t="n">
-        <v>58.94477182043742</v>
+        <v>38.27258957236691</v>
       </c>
       <c r="C31" t="n">
-        <v>48.77169934701083</v>
+        <v>45.62679137149805</v>
       </c>
       <c r="D31" t="n">
-        <v>6.420997873822294</v>
+        <v>6.454590375597124</v>
       </c>
       <c r="E31" t="n">
-        <v>4.76234247464976</v>
+        <v>4.406388988468396</v>
       </c>
       <c r="F31" t="n">
-        <v>10.3015914721062</v>
+        <v>9.993116367619507</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1645318921519839</v>
+        <v>0.1735495377115714</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1894919898594385</v>
+        <v>-0.01887161948433885</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6878656539811349</v>
+        <v>-0.637548364442725</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6282354896432392</v>
+        <v>-0.5219041427696453</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1439004684469335</v>
+        <v>-0.00384417068758095</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.7023607007690261</v>
+        <v>-0.03759250950582512</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07642142595993244</v>
+        <v>-0.04584539014502856</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88.53058240800844</v>
+        <v>85.84251762379158</v>
       </c>
       <c r="B32" t="n">
-        <v>82.81618193075175</v>
+        <v>66.43481520921625</v>
       </c>
       <c r="C32" t="n">
-        <v>48.78422224758449</v>
+        <v>45.41889759472295</v>
       </c>
       <c r="D32" t="n">
-        <v>10.94554732451241</v>
+        <v>11.70830947110029</v>
       </c>
       <c r="E32" t="n">
-        <v>2.424355066836205</v>
+        <v>4.24493963784002</v>
       </c>
       <c r="F32" t="n">
-        <v>13.74847599123865</v>
+        <v>13.28919437891046</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06693853929656127</v>
+        <v>0.07336808445277941</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6176079291602626</v>
+        <v>-0.526188430555833</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8294396928058969</v>
+        <v>-0.7970832444051259</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8623023884193933</v>
+        <v>-0.8176541353011113</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.03155027108801165</v>
+        <v>-0.02395674214470674</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5363296238200543</v>
+        <v>-0.2801575696356984</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.07705618235035079</v>
+        <v>-0.0004867479395530283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>93.09217172275477</v>
+        <v>98.73537233456921</v>
       </c>
       <c r="B33" t="n">
-        <v>83.69037780418101</v>
+        <v>56.84584976067474</v>
       </c>
       <c r="C33" t="n">
-        <v>48.78281891934812</v>
+        <v>45.42022584810854</v>
       </c>
       <c r="D33" t="n">
-        <v>10.94554732451241</v>
+        <v>10.59489130636116</v>
       </c>
       <c r="E33" t="n">
-        <v>2.538695283891665</v>
+        <v>4.804784306880613</v>
       </c>
       <c r="F33" t="n">
-        <v>14.91104948606621</v>
+        <v>16.38046354816856</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05610057893744084</v>
+        <v>0.04480096013381068</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6691059682209418</v>
+        <v>-0.6812243712664749</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8489629833914976</v>
+        <v>-0.8536283816417392</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8863012127533941</v>
+        <v>-0.8919152717562964</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1698247926609436</v>
+        <v>-0.08599277678715875</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5704050140805603</v>
+        <v>-0.5784895278838055</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.07696034540893847</v>
+        <v>-0.0007765486782257414</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68.13547898368438</v>
+        <v>69.32460379487904</v>
       </c>
       <c r="B34" t="n">
-        <v>85.30572808313548</v>
+        <v>36.26952571226197</v>
       </c>
       <c r="C34" t="n">
-        <v>47.1991098112715</v>
+        <v>45.42704242637706</v>
       </c>
       <c r="D34" t="n">
-        <v>6.487157393711655</v>
+        <v>6.285655164916056</v>
       </c>
       <c r="E34" t="n">
-        <v>4.760577695734013</v>
+        <v>4.896868119882379</v>
       </c>
       <c r="F34" t="n">
-        <v>10.23317777105878</v>
+        <v>10.60081849224685</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1645845022611369</v>
+        <v>0.1511299845075559</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1896699096899939</v>
+        <v>-0.1213462604924483</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6878900240175062</v>
+        <v>-0.6676101864508391</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6283282660487018</v>
+        <v>-0.5870272716105202</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.005041885583952179</v>
+        <v>-0.01753058002880127</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6918638411551381</v>
+        <v>-0.005901099786038144</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.07829692649350964</v>
+        <v>-0.002263802118630948</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>75.06902064856499</v>
+        <v>89.13353699139427</v>
       </c>
       <c r="B35" t="n">
-        <v>123.5830056262728</v>
+        <v>62.40069570550187</v>
       </c>
       <c r="C35" t="n">
-        <v>49.54393824371189</v>
+        <v>45.6030738038077</v>
       </c>
       <c r="D35" t="n">
-        <v>12.91094022725805</v>
+        <v>11.04248891295846</v>
       </c>
       <c r="E35" t="n">
-        <v>4.053558163994591</v>
+        <v>4.627801117999313</v>
       </c>
       <c r="F35" t="n">
-        <v>11.18282680863775</v>
+        <v>13.95096436116715</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1223910202263818</v>
+        <v>0.06406653633883586</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3812997829145423</v>
+        <v>-0.575192078163167</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7466964228756223</v>
+        <v>-0.8145917739686961</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7392746318947593</v>
+        <v>-0.8422155324154671</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02486607295355809</v>
+        <v>-0.0126111760740612</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.4357708188031132</v>
+        <v>-0.1375467303729152</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1055195389913937</v>
+        <v>-0.04067064810349727</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>91.56753701568016</v>
+        <v>95.46533278577384</v>
       </c>
       <c r="B36" t="n">
-        <v>97.6489260152711</v>
+        <v>61.1216738956973</v>
       </c>
       <c r="C36" t="n">
-        <v>48.27786541356354</v>
+        <v>45.42014298648863</v>
       </c>
       <c r="D36" t="n">
-        <v>10.37583237743028</v>
+        <v>11.19035509132485</v>
       </c>
       <c r="E36" t="n">
-        <v>4.627325303504235</v>
+        <v>4.02578126642072</v>
       </c>
       <c r="F36" t="n">
-        <v>14.39870120795707</v>
+        <v>15.62873519412523</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05934272283990761</v>
+        <v>0.05041508411728268</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6531612415931652</v>
+        <v>-0.6486561491564427</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8428817270345458</v>
+        <v>-0.8410410174410089</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8790046050535764</v>
+        <v>-0.8770497712871451</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.01470586281356651</v>
+        <v>-0.08339009796185631</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5590158865060258</v>
+        <v>-0.5551904960986387</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.06727428753666688</v>
+        <v>-0.0007584697793371065</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>81.86038049064109</v>
+        <v>85.48217672477854</v>
       </c>
       <c r="B37" t="n">
-        <v>96.67173977055521</v>
+        <v>66.43481520921625</v>
       </c>
       <c r="C37" t="n">
-        <v>47.33879520114911</v>
+        <v>45.41889759472295</v>
       </c>
       <c r="D37" t="n">
-        <v>12.15794239755277</v>
+        <v>11.70830947110029</v>
       </c>
       <c r="E37" t="n">
-        <v>3.736284727056357</v>
+        <v>4.24493963784002</v>
       </c>
       <c r="F37" t="n">
-        <v>12.44652326181895</v>
+        <v>13.20191816262268</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08895978878797511</v>
+        <v>0.07447496882700148</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5197236638004414</v>
+        <v>-0.5203727221144929</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7939059600823596</v>
+        <v>-0.7950396460560206</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8137048794146193</v>
+        <v>-0.8146826966936881</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.02189062218205255</v>
+        <v>-0.01365722545835552</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4865027503845385</v>
+        <v>-0.2957723419262631</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.08343161446983169</v>
+        <v>-0.0004867479395530283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>90.65422654096368</v>
+        <v>75.96229335524694</v>
       </c>
       <c r="B38" t="n">
-        <v>75.84112008522328</v>
+        <v>38.08377189014391</v>
       </c>
       <c r="C38" t="n">
-        <v>48.78075461422551</v>
+        <v>46.73474945664135</v>
       </c>
       <c r="D38" t="n">
-        <v>10.71827662721743</v>
+        <v>5.000812813305338</v>
       </c>
       <c r="E38" t="n">
-        <v>3.781051067567836</v>
+        <v>2.10992173247367</v>
       </c>
       <c r="F38" t="n">
-        <v>14.2251999463311</v>
+        <v>12.13874609006941</v>
       </c>
       <c r="G38" t="n">
-        <v>0.06151968222125445</v>
+        <v>0.1082297464580397</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6429353350835465</v>
+        <v>-0.3260092855081791</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8389742078858008</v>
+        <v>-0.7304198468423305</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8742535645396463</v>
+        <v>-0.7093295589715491</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.05719614840748787</v>
+        <v>-0.1088879516954453</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5521933935748088</v>
+        <v>-0.4550929767551428</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0768193686338937</v>
+        <v>-0.2875816996308412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>82.23630395140633</v>
+        <v>74.64471627426681</v>
       </c>
       <c r="B39" t="n">
-        <v>80.39010975174673</v>
+        <v>43.97905362889126</v>
       </c>
       <c r="C39" t="n">
-        <v>48.68911147372419</v>
+        <v>45.4338042995362</v>
       </c>
       <c r="D39" t="n">
-        <v>11.82747545810806</v>
+        <v>5.254955471070101</v>
       </c>
       <c r="E39" t="n">
-        <v>4.628178480189673</v>
+        <v>3.967925817770506</v>
       </c>
       <c r="F39" t="n">
-        <v>12.47318144047397</v>
+        <v>11.7919231701849</v>
       </c>
       <c r="G39" t="n">
-        <v>0.08741533719726209</v>
+        <v>0.1152835022942207</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.526186709871493</v>
+        <v>-0.290672168888559</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7962112842262865</v>
+        <v>-0.7191768204868497</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8170316080537832</v>
+        <v>-0.6889451994230569</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.004868421466433421</v>
+        <v>-0.01259280574395332</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4893109248495752</v>
+        <v>-0.516579907200882</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.07243782551647175</v>
+        <v>-0.003739119898807236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98.24091806996819</v>
+        <v>82.73521770575195</v>
       </c>
       <c r="B40" t="n">
-        <v>199.3368094922656</v>
+        <v>70.46889586378218</v>
       </c>
       <c r="C40" t="n">
-        <v>49.51680215869968</v>
+        <v>45.430114636372</v>
       </c>
       <c r="D40" t="n">
-        <v>9.269680462347452</v>
+        <v>12.0831709782355</v>
       </c>
       <c r="E40" t="n">
-        <v>3.393962079527388</v>
+        <v>4.587725313675631</v>
       </c>
       <c r="F40" t="n">
-        <v>15.89374662580985</v>
+        <v>12.64133026476034</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04630918884588038</v>
+        <v>0.08382619577320978</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7167630049679657</v>
+        <v>-0.4725634518647653</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8678047962993938</v>
+        <v>-0.7784534011290357</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9074730159147147</v>
+        <v>-0.7898046135175714</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.0744528448423598</v>
+        <v>-0.0003147916892003195</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.6088665083160204</v>
+        <v>-0.414807232750749</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1062816606780354</v>
+        <v>-0.002934102481164241</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66.8267958928482</v>
+        <v>67.8892877414149</v>
       </c>
       <c r="B41" t="n">
-        <v>53.04962460125667</v>
+        <v>42.14511076878059</v>
       </c>
       <c r="C41" t="n">
-        <v>49.20031273419678</v>
+        <v>45.42485364006175</v>
       </c>
       <c r="D41" t="n">
-        <v>6.487884151160434</v>
+        <v>6.65928613988149</v>
       </c>
       <c r="E41" t="n">
-        <v>4.706870727053356</v>
+        <v>2.131298797263796</v>
       </c>
       <c r="F41" t="n">
-        <v>9.994844207591386</v>
+        <v>10.3211605669949</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1766386910570758</v>
+        <v>0.1633243326809872</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1424329491111926</v>
+        <v>-0.06565442092362445</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6736310306473406</v>
+        <v>-0.6511466272215704</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5993174554323087</v>
+        <v>-0.5519183814815857</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.07012252448086558</v>
+        <v>-0.01490540511342854</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6937340667982829</v>
+        <v>-0.06271569356899413</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1032321454138883</v>
+        <v>-0.001786248740744678</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>88.81076310106887</v>
+        <v>84.50969717960591</v>
       </c>
       <c r="B42" t="n">
-        <v>82.99224762499718</v>
+        <v>68.3391733158313</v>
       </c>
       <c r="C42" t="n">
-        <v>48.78332425250461</v>
+        <v>46.50631316640135</v>
       </c>
       <c r="D42" t="n">
-        <v>11.16329916786017</v>
+        <v>11.78949071638648</v>
       </c>
       <c r="E42" t="n">
-        <v>3.87741261548568</v>
+        <v>4.839236949644354</v>
       </c>
       <c r="F42" t="n">
-        <v>13.87285298528453</v>
+        <v>13.05735062560492</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06624968354347339</v>
+        <v>0.07768868843720671</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6210004633354258</v>
+        <v>-0.5041036417977782</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8306851022187305</v>
+        <v>-0.7893387433683022</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8639112897791961</v>
+        <v>-0.8062998702659496</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.07704974917087311</v>
+        <v>-0.02296337206266071</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5384225931341989</v>
+        <v>-0.3379131222170775</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0769948559267602</v>
+        <v>-0.2377410544875667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>87.19383145836304</v>
+        <v>76.6806232961148</v>
       </c>
       <c r="B43" t="n">
-        <v>121.5834315679875</v>
+        <v>71.3492619180691</v>
       </c>
       <c r="C43" t="n">
-        <v>48.79166205371033</v>
+        <v>45.43596500968627</v>
       </c>
       <c r="D43" t="n">
-        <v>11.01993956868493</v>
+        <v>5.141207553161942</v>
       </c>
       <c r="E43" t="n">
-        <v>2.677673498605935</v>
+        <v>3.767065700638401</v>
       </c>
       <c r="F43" t="n">
-        <v>13.4379409821282</v>
+        <v>12.34480121798597</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07066535938621128</v>
+        <v>0.1046383914325755</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.6004089556456912</v>
+        <v>-0.3442483538263195</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.8230605421028018</v>
+        <v>-0.7362797216013729</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.8540378962989739</v>
+        <v>-0.7197125213418493</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.00471808291186514</v>
+        <v>-0.2224999737871539</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5263440010146393</v>
+        <v>-0.4215709128479759</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.07756426609392679</v>
+        <v>-0.004210547567912865</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>98.68835570580958</v>
+        <v>93.46879215538428</v>
       </c>
       <c r="B44" t="n">
-        <v>118.3008251083189</v>
+        <v>56.68190034370113</v>
       </c>
       <c r="C44" t="n">
-        <v>49.51804548868092</v>
+        <v>45.56163430804902</v>
       </c>
       <c r="D44" t="n">
-        <v>9.087930789946693</v>
+        <v>10.76538955990238</v>
       </c>
       <c r="E44" t="n">
-        <v>2.301452821795104</v>
+        <v>4.825482258414506</v>
       </c>
       <c r="F44" t="n">
-        <v>15.9713875570591</v>
+        <v>14.99945509195334</v>
       </c>
       <c r="G44" t="n">
-        <v>0.04556651438176411</v>
+        <v>0.05419023524663946</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7204538081999382</v>
+        <v>-0.6296289850325056</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8692961900720924</v>
+        <v>-0.834629293654287</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9090670583939315</v>
+        <v>-0.8684151759050203</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.05651247570022604</v>
+        <v>-0.02759226262715062</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.6122088986555553</v>
+        <v>-0.05353988677266368</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.1062467415383762</v>
+        <v>-0.03162930357433133</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>64.43271793039879</v>
+        <v>94.40589256178168</v>
       </c>
       <c r="B45" t="n">
-        <v>58.70867266104628</v>
+        <v>51.20984308834988</v>
       </c>
       <c r="C45" t="n">
-        <v>48.79590591808366</v>
+        <v>45.42013006578996</v>
       </c>
       <c r="D45" t="n">
-        <v>7.100067121587557</v>
+        <v>10.76538955990238</v>
       </c>
       <c r="E45" t="n">
-        <v>2.403583256635048</v>
+        <v>4.3289872486314</v>
       </c>
       <c r="F45" t="n">
-        <v>9.552090732286306</v>
+        <v>15.24012435803313</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2024646696279301</v>
+        <v>0.0523358540050864</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04522781221687782</v>
+        <v>-0.6401165815168405</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6448341154957042</v>
+        <v>-0.8385701728977499</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5378931155620261</v>
+        <v>-0.8733240148391225</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.06398792916038823</v>
+        <v>-0.05545273191214135</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6778372407374734</v>
+        <v>-0.01397342516921807</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.07785409064870245</v>
+        <v>-0.0007556507178098359</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>75.4074262123078</v>
+        <v>67.9100630060161</v>
       </c>
       <c r="B46" t="n">
-        <v>125.3040279871047</v>
+        <v>42.16258402206069</v>
       </c>
       <c r="C46" t="n">
-        <v>47.8681034340925</v>
+        <v>45.42521866296772</v>
       </c>
       <c r="D46" t="n">
-        <v>12.92242810999485</v>
+        <v>6.667612248706873</v>
       </c>
       <c r="E46" t="n">
-        <v>4.030038792251535</v>
+        <v>2.131298797263796</v>
       </c>
       <c r="F46" t="n">
-        <v>11.239991187628</v>
+        <v>10.32853401981358</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1203587604617757</v>
+        <v>0.1631449140828338</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.3894119367924159</v>
+        <v>-0.06649005530140498</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7493826830780838</v>
+        <v>-0.6513909410298532</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.743804389845247</v>
+        <v>-0.5524498744711305</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.0002297129725747818</v>
+        <v>-0.01895155043827922</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4382987319612718</v>
+        <v>-0.06189333934519611</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.07848712979661719</v>
+        <v>-0.001865890102046852</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>92.06665317259977</v>
+        <v>89.13353699139427</v>
       </c>
       <c r="B47" t="n">
-        <v>140.1373683549697</v>
+        <v>62.40069570550187</v>
       </c>
       <c r="C47" t="n">
-        <v>49.28595731650982</v>
+        <v>45.6030738038077</v>
       </c>
       <c r="D47" t="n">
-        <v>10.71827662721743</v>
+        <v>11.04248891295846</v>
       </c>
       <c r="E47" t="n">
-        <v>3.80358512949543</v>
+        <v>4.469399040483751</v>
       </c>
       <c r="F47" t="n">
-        <v>14.60709851303032</v>
+        <v>13.95096436116715</v>
       </c>
       <c r="G47" t="n">
-        <v>0.05828817703613853</v>
+        <v>0.06406653633883586</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6584455495922165</v>
+        <v>-0.575192078163167</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8448756848056502</v>
+        <v>-0.8145917739686961</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8814310395004756</v>
+        <v>-0.8422155324154671</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1109965525041943</v>
+        <v>-0.0126111760740612</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5627443190015552</v>
+        <v>-0.1375467303729152</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1067416163242133</v>
+        <v>-0.04067064810349727</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>80.14208359347192</v>
+        <v>67.41106256274905</v>
       </c>
       <c r="B48" t="n">
-        <v>197.8771289250576</v>
+        <v>44.97480287028736</v>
       </c>
       <c r="C48" t="n">
-        <v>47.94956272483807</v>
+        <v>45.56462699617015</v>
       </c>
       <c r="D48" t="n">
-        <v>12.60527188980373</v>
+        <v>6.361974189103123</v>
       </c>
       <c r="E48" t="n">
-        <v>3.336128553549536</v>
+        <v>4.479539184065576</v>
       </c>
       <c r="F48" t="n">
-        <v>12.19891217298674</v>
+        <v>10.13106930212433</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09628148253258494</v>
+        <v>0.1674869331767377</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.4888761747691161</v>
+        <v>-0.04616290969903779</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7830691649157895</v>
+        <v>-0.6454694942429231</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.7976482752883322</v>
+        <v>-0.5394805651200575</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.06144387674661241</v>
+        <v>-0.0283765305017113</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4736669527459447</v>
+        <v>-0.01142558338832015</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.07750682560247356</v>
+        <v>-0.03228225370985119</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>78.7443590856398</v>
+        <v>93.87058561681299</v>
       </c>
       <c r="B49" t="n">
-        <v>84.21196854525505</v>
+        <v>36.67204291668484</v>
       </c>
       <c r="C49" t="n">
-        <v>48.56989319353263</v>
+        <v>45.53720444421145</v>
       </c>
       <c r="D49" t="n">
-        <v>12.60527188980373</v>
+        <v>10.64962156865388</v>
       </c>
       <c r="E49" t="n">
-        <v>2.417988352641927</v>
+        <v>4.419661982821182</v>
       </c>
       <c r="F49" t="n">
-        <v>11.88209995103772</v>
+        <v>15.07598036571777</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1026217844115051</v>
+        <v>0.05336564514086593</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4620287762893439</v>
+        <v>-0.6341887181971905</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7738335115728281</v>
+        <v>-0.8363424451283432</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.78343372108723</v>
+        <v>-0.8705561384791579</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.04124103985118067</v>
+        <v>-0.01933031107977088</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4632258532091921</v>
+        <v>-0.03657527395678502</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.06803527695846105</v>
+        <v>-0.02629915146431572</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99.83688828311152</v>
+        <v>90.64010257391644</v>
       </c>
       <c r="B50" t="n">
-        <v>89.36715868675756</v>
+        <v>40.572498385236</v>
       </c>
       <c r="C50" t="n">
-        <v>49.08290896430322</v>
+        <v>45.42492484772082</v>
       </c>
       <c r="D50" t="n">
-        <v>8.680685594061021</v>
+        <v>10.87786338401564</v>
       </c>
       <c r="E50" t="n">
-        <v>3.797771259692285</v>
+        <v>4.500278561727275</v>
       </c>
       <c r="F50" t="n">
-        <v>16.17506090727832</v>
+        <v>14.28285181566801</v>
       </c>
       <c r="G50" t="n">
-        <v>0.04373586140074749</v>
+        <v>0.06035413852913724</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.7296239636197231</v>
+        <v>-0.5953026576874346</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8730204745838327</v>
+        <v>-0.8219189381880844</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9129970719997986</v>
+        <v>-0.8520326368511443</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01189561196094713</v>
+        <v>-0.02844038810350894</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.620788517095109</v>
+        <v>-0.07226222179695449</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.09561117716752658</v>
+        <v>-0.001801784957269764</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>66.32814377492041</v>
+        <v>90.64010257391644</v>
       </c>
       <c r="B51" t="n">
-        <v>53.60465677529334</v>
+        <v>38.22124511879691</v>
       </c>
       <c r="C51" t="n">
-        <v>48.78061529460103</v>
+        <v>45.42492484772082</v>
       </c>
       <c r="D51" t="n">
-        <v>6.420997873822294</v>
+        <v>10.87786338401564</v>
       </c>
       <c r="E51" t="n">
-        <v>4.932254329731843</v>
+        <v>4.500278561727275</v>
       </c>
       <c r="F51" t="n">
-        <v>9.844713280835576</v>
+        <v>14.28285181566801</v>
       </c>
       <c r="G51" t="n">
-        <v>0.181522188988533</v>
+        <v>0.06035413852913724</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.123462740981512</v>
+        <v>-0.5953026576874346</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6679664649796788</v>
+        <v>-0.8219189381880844</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.5875193782488144</v>
+        <v>-0.8520326368511443</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.003587734399609513</v>
+        <v>-0.02844038810350894</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.6904229858277022</v>
+        <v>-0.07226222179695449</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.07680985413376208</v>
+        <v>-0.001801784957269764</v>
       </c>
     </row>
   </sheetData>
